--- a/Resources/Sheet/Book3.xlsx
+++ b/Resources/Sheet/Book3.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A8CB15-A0A0-46D2-82FE-A6B4F98F99E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73D00F6-AFD8-4442-9ECD-A17E0F08609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="2805" windowWidth="21600" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoDamQuanY" sheetId="16" r:id="rId1"/>
+    <sheet name="ChiLenhHCKT" sheetId="17" r:id="rId2"/>
+    <sheet name="PhanCapVCHC" sheetId="18" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
   <si>
     <t>+</t>
   </si>
@@ -96,13 +98,232 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>1. Quy định dự trữ, tiêu thụ, bổ sung vật chất</t>
+  </si>
+  <si>
+    <t>Đạn, vật chất hậu cần, vật tư kỹ thuật</t>
+  </si>
+  <si>
+    <t>ĐVT</t>
+  </si>
+  <si>
+    <t>Quy định dự trữ</t>
+  </si>
+  <si>
+    <t>Phải có 04.00-N</t>
+  </si>
+  <si>
+    <t>Phải có SCĐ</t>
+  </si>
+  <si>
+    <t>Tiêu thụ</t>
+  </si>
+  <si>
+    <t>GĐCB</t>
+  </si>
+  <si>
+    <t>GĐCĐ</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Đạn</t>
+  </si>
+  <si>
+    <t>Đạn K51 (SN)</t>
+  </si>
+  <si>
+    <t>Cơ số</t>
+  </si>
+  <si>
+    <t>Đạn K56 (TL, TrL)</t>
+  </si>
+  <si>
+    <t>Đạn K53 (ĐL)</t>
+  </si>
+  <si>
+    <t>Đạn 12,7 mm</t>
+  </si>
+  <si>
+    <t>Đạn cối 100 mm</t>
+  </si>
+  <si>
+    <t>Đạn cối 82 mm</t>
+  </si>
+  <si>
+    <t>Đạn cối 60 mm</t>
+  </si>
+  <si>
+    <t>Đạn SPG-9</t>
+  </si>
+  <si>
+    <t>Đạn B41</t>
+  </si>
+  <si>
+    <t>Lựu đạn</t>
+  </si>
+  <si>
+    <t>Quả</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Vật chất hậu cần</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Quân nhu</t>
+  </si>
+  <si>
+    <t>LTTP</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Lương khô</t>
+  </si>
+  <si>
+    <t>ĐSTB</t>
+  </si>
+  <si>
+    <t>QLCĐ</t>
+  </si>
+  <si>
+    <t>QTCĐ</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Quân y</t>
+  </si>
+  <si>
+    <t>Túi y sỹ</t>
+  </si>
+  <si>
+    <t>Túi</t>
+  </si>
+  <si>
+    <t>Túi y tá</t>
+  </si>
+  <si>
+    <t>Túi cứu thương</t>
+  </si>
+  <si>
+    <t>Băng cá nhân</t>
+  </si>
+  <si>
+    <t>C/ng</t>
+  </si>
+  <si>
+    <t>Doanh Trại</t>
+  </si>
+  <si>
+    <t>Dầu thắp</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Vật tư kỹ thuật</t>
+  </si>
+  <si>
+    <t>Tấn</t>
+  </si>
+  <si>
+    <t>2. Dự kiến tỉ lệ thương binh, bệnh binh</t>
+  </si>
+  <si>
+    <t>Tỷ lệ thương binh toàn trận</t>
+  </si>
+  <si>
+    <t>Tỷ lệ thương binh trung bình ngày đêm</t>
+  </si>
+  <si>
+    <t>Tỷ lệ thương binh ngày cao nhất</t>
+  </si>
+  <si>
+    <t>Tỷ lệ thương binh phải càng</t>
+  </si>
+  <si>
+    <t>Tỷ lệ bệnh binh toàn trận</t>
+  </si>
+  <si>
+    <t>3. Dự kiến tỉ lệ vũ khí trang bị hư hỏng</t>
+  </si>
+  <si>
+    <t>SMPK 12,7mm</t>
+  </si>
+  <si>
+    <t>Súng SPG-9</t>
+  </si>
+  <si>
+    <t>Súng cối các loại</t>
+  </si>
+  <si>
+    <t>Súng bộ binh</t>
+  </si>
+  <si>
+    <t>2. Phân cấp một số loại vật chất hậu cần chủ yếu</t>
+  </si>
+  <si>
+    <t>Loại Vật chất</t>
+  </si>
+  <si>
+    <t>Phải có 04.00N</t>
+  </si>
+  <si>
+    <t>Phải có sau chiến đấu</t>
+  </si>
+  <si>
+    <t>Kho d</t>
+  </si>
+  <si>
+    <t>Đơn vị</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>Gạo, thực phẩm</t>
+  </si>
+  <si>
+    <t>Ngày ăn</t>
+  </si>
+  <si>
+    <t>Đường sữa thương binh</t>
+  </si>
+  <si>
+    <t>Quân lương chiến đấu</t>
+  </si>
+  <si>
+    <t>Quân trang chiến đấu</t>
+  </si>
+  <si>
+    <t>C/người</t>
+  </si>
+  <si>
+    <t>Doanh trại</t>
+  </si>
+  <si>
+    <t>II.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,8 +355,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,8 +421,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -258,15 +531,154 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -276,25 +688,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -576,358 +988,358 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="2" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="2" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="29"/>
+      <c r="J2" s="24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="1" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="29"/>
+      <c r="H3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="6"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7" t="s">
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="8">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="9">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
         <f>ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
         <f>ROUND(E5*F5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9">
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
         <f>ROUND(H5*C5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="3">
         <f>E5+I5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
         <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="4">
         <v>1</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="3">
         <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="4">
         <v>1</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="3">
         <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="3">
         <f t="shared" ref="J6:J11" si="3">E6+I6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="4">
         <v>2</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="4">
         <v>2</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="36">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="9">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="4">
         <v>3</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="4">
         <v>3</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="4">
         <v>4</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="4">
         <v>4</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="24">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="4">
         <v>5</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="4">
         <v>5</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="9">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="4">
         <v>6</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="4">
         <v>6</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24">
-      <c r="A12" s="8">
+      <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="3">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="4">
         <v>8</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="3">
         <f>ROUND(C12*D12/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="5"/>
+      <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -946,4 +1358,1382 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDF17EA-1061-464B-883E-6391396F7EEA}">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18.75">
+      <c r="A1" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="18.75">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="37.5">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75">
+      <c r="A4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" ht="18.75">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75">
+      <c r="A6" s="8">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75">
+      <c r="A7" s="8">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75">
+      <c r="A8" s="8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18.75">
+      <c r="A9" s="8">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75">
+      <c r="A10" s="8">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75">
+      <c r="A11" s="8">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75">
+      <c r="A12" s="8">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75">
+      <c r="A13" s="8">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75">
+      <c r="A14" s="8">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75">
+      <c r="A16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75">
+      <c r="A17" s="8">
+        <v>1</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="18.75">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.75">
+      <c r="A19" s="8">
+        <v>3</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="18.75">
+      <c r="A20" s="8">
+        <v>4</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18.75">
+      <c r="A21" s="8">
+        <v>5</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18.75">
+      <c r="A22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18.75">
+      <c r="A23" s="8">
+        <v>7</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18.75">
+      <c r="A24" s="8">
+        <v>8</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18.75">
+      <c r="A25" s="8">
+        <v>9</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18.75">
+      <c r="A26" s="8">
+        <v>10</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18.75">
+      <c r="A27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="18.75">
+      <c r="A28" s="8">
+        <v>12</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="18.75">
+      <c r="A29" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="18.75">
+      <c r="A30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8" ht="18.75">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="12">
+        <v>20</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8" ht="37.5">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" ht="18.75">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="12">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" ht="18.75">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="12">
+        <v>50</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8" ht="18.75">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8" ht="18.75">
+      <c r="A36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" ht="18.75">
+      <c r="A37" s="13"/>
+      <c r="B37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="12">
+        <v>8</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" ht="18.75">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" ht="18.75">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="12">
+        <v>9</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" ht="18.75">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D025E2D6-EA1E-4D0C-8531-FB2A59F3BA70}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21" thickBot="1">
+      <c r="A1" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A4" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A5" s="16"/>
+      <c r="B5" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A6" s="20">
+        <v>1</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="22">
+        <f>F6-E6</f>
+        <v>-5</v>
+      </c>
+      <c r="E6" s="23">
+        <v>5</v>
+      </c>
+      <c r="F6" s="22">
+        <f>ChiLenhHCKT!E17</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="22">
+        <f>I6-H6</f>
+        <v>-3</v>
+      </c>
+      <c r="H6" s="23">
+        <v>3</v>
+      </c>
+      <c r="I6" s="22">
+        <f>ChiLenhHCKT!F17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A7" s="20">
+        <v>2</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="22">
+        <f t="shared" ref="D7:D18" si="0">F7-E7</f>
+        <v>-2</v>
+      </c>
+      <c r="E7" s="23">
+        <v>2</v>
+      </c>
+      <c r="F7" s="22">
+        <f>ChiLenhHCKT!E18</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="22">
+        <f t="shared" ref="G7:G18" si="1">I7-H7</f>
+        <v>-1</v>
+      </c>
+      <c r="H7" s="23">
+        <v>1</v>
+      </c>
+      <c r="I7" s="22">
+        <f>ChiLenhHCKT!F18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A8" s="20">
+        <v>3</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="22">
+        <f t="shared" si="0"/>
+        <v>-11</v>
+      </c>
+      <c r="E8" s="23">
+        <v>11</v>
+      </c>
+      <c r="F8" s="22">
+        <f>ChiLenhHCKT!E19</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+      <c r="H8" s="23">
+        <v>5</v>
+      </c>
+      <c r="I8" s="22">
+        <f>ChiLenhHCKT!F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A9" s="20">
+        <v>4</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="22">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+      <c r="E9" s="23">
+        <v>100</v>
+      </c>
+      <c r="F9" s="22">
+        <f>ChiLenhHCKT!E20</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="1"/>
+        <v>-100</v>
+      </c>
+      <c r="H9" s="23">
+        <v>100</v>
+      </c>
+      <c r="I9" s="22">
+        <f>ChiLenhHCKT!F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A10" s="20">
+        <v>5</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="22">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+      <c r="E10" s="23">
+        <v>100</v>
+      </c>
+      <c r="F10" s="22">
+        <f>ChiLenhHCKT!E21</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="22">
+        <f t="shared" si="1"/>
+        <v>-100</v>
+      </c>
+      <c r="H10" s="23">
+        <v>100</v>
+      </c>
+      <c r="I10" s="22">
+        <f>ChiLenhHCKT!F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A11" s="20"/>
+      <c r="B11" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="22">
+        <f>ChiLenhHCKT!E22</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="22">
+        <f>ChiLenhHCKT!F22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A12" s="20">
+        <v>7</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="22">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3</v>
+      </c>
+      <c r="F12" s="22">
+        <f>ChiLenhHCKT!E23</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="H12" s="23">
+        <v>1</v>
+      </c>
+      <c r="I12" s="22">
+        <f>ChiLenhHCKT!F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A13" s="20">
+        <v>8</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="22">
+        <f t="shared" si="0"/>
+        <v>-16</v>
+      </c>
+      <c r="E13" s="23">
+        <v>16</v>
+      </c>
+      <c r="F13" s="22">
+        <f>ChiLenhHCKT!E24</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <f t="shared" si="1"/>
+        <v>-6</v>
+      </c>
+      <c r="H13" s="23">
+        <v>6</v>
+      </c>
+      <c r="I13" s="22">
+        <f>ChiLenhHCKT!F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A14" s="20">
+        <v>9</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="22">
+        <f t="shared" si="0"/>
+        <v>-23</v>
+      </c>
+      <c r="E14" s="23">
+        <v>23</v>
+      </c>
+      <c r="F14" s="22">
+        <f>ChiLenhHCKT!E25</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" si="1"/>
+        <v>-9</v>
+      </c>
+      <c r="H14" s="23">
+        <v>9</v>
+      </c>
+      <c r="I14" s="22">
+        <f>ChiLenhHCKT!F25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A15" s="20">
+        <v>10</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="22">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
+      <c r="F15" s="22">
+        <f>ChiLenhHCKT!E26</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="H15" s="23">
+        <v>1</v>
+      </c>
+      <c r="I15" s="22">
+        <f>ChiLenhHCKT!F26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A16" s="20"/>
+      <c r="B16" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="22">
+        <f>ChiLenhHCKT!E27</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="22">
+        <f>ChiLenhHCKT!F27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A17" s="20">
+        <v>11</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="22">
+        <f t="shared" si="0"/>
+        <v>-5</v>
+      </c>
+      <c r="E17" s="23">
+        <v>5</v>
+      </c>
+      <c r="F17" s="22">
+        <f>ChiLenhHCKT!E28</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="22">
+        <f t="shared" si="1"/>
+        <v>-3</v>
+      </c>
+      <c r="H17" s="23">
+        <v>3</v>
+      </c>
+      <c r="I17" s="22">
+        <f>ChiLenhHCKT!F28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="22">
+        <f t="shared" si="0"/>
+        <v>-0.1</v>
+      </c>
+      <c r="E18" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="22">
+        <f>ChiLenhHCKT!E29</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <f t="shared" si="1"/>
+        <v>-0.1</v>
+      </c>
+      <c r="H18" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="22">
+        <f>ChiLenhHCKT!F29</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Resources/Sheet/Book3.xlsx
+++ b/Resources/Sheet/Book3.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73D00F6-AFD8-4442-9ECD-A17E0F08609A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B847B020-C3CD-4CC0-AC5C-FDE5A25AD3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="4140" windowWidth="21600" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoDamQuanY" sheetId="16" r:id="rId1"/>
     <sheet name="ChiLenhHCKT" sheetId="17" r:id="rId2"/>
     <sheet name="PhanCapVCHC" sheetId="18" r:id="rId3"/>
+    <sheet name="KeHoachBaoDamQuanY" sheetId="20" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
   <si>
     <t>+</t>
   </si>
@@ -317,13 +318,28 @@
   </si>
   <si>
     <t>II.</t>
+  </si>
+  <si>
+    <t>Phân bổ chuyển thương</t>
+  </si>
+  <si>
+    <t>Cáng bộ</t>
+  </si>
+  <si>
+    <t>Tự đi</t>
+  </si>
+  <si>
+    <t>Hướng Chủ yếu</t>
+  </si>
+  <si>
+    <t>Hướng Thứ Yếu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,8 +411,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,6 +454,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -670,6 +700,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -708,6 +739,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -984,83 +1033,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68878A65-A8E3-488E-8D20-235E1B05D76B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="27" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="29"/>
-      <c r="J2" s="24" t="s">
+      <c r="I2" s="30"/>
+      <c r="J2" s="25" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="25"/>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
       <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1106,7 +1155,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -1115,25 +1164,25 @@
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
+        <f t="shared" ref="E6:E9" si="0">ROUND(C6*D6/100,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
+        <f t="shared" ref="G6:G9" si="1">ROUND(E6*F6/100,0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
+        <f t="shared" ref="I6:I9" si="2">ROUND(H6*C6/100,0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
+        <f t="shared" ref="J6:J9" si="3">E6+I6</f>
         <v>0</v>
       </c>
     </row>
@@ -1142,7 +1191,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -1173,12 +1222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="36">
+    <row r="8" spans="1:10" ht="24">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -1191,14 +1240,14 @@
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="2"/>
@@ -1209,12 +1258,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="24">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -1227,14 +1274,14 @@
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="2"/>
@@ -1246,100 +1293,30 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="24">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
+      <c r="A10" s="2">
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3">
+        <f>C5</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>6</v>
-      </c>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>6</v>
-      </c>
-      <c r="I11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="24">
-      <c r="A12" s="2">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3">
-        <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3">
-        <f>ROUND(C12*D12/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="2" t="s">
+        <f>ROUND(C10*D10/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1371,48 +1348,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" ht="18.75">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="31"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:8" ht="37.5">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
@@ -2254,30 +2231,30 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="34" t="s">
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9" ht="19.5" thickBot="1">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="17" t="s">
         <v>83</v>
       </c>
@@ -2736,4 +2713,457 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE6020-7C21-4FFE-A7B3-EC73B1C2094F}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="26"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <f>ROUND(C5*D5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <f>ROUND(E5*F5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <f>ROUND(H5*C5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <f>E5+I5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="24">
+        <f>ROUNDUP(J5/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="24">
+        <f>J5-K5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="24">
+        <f>J5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="24">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3">
+        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="3">
+        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3">
+        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
+        <f t="shared" ref="K6:K11" si="4">ROUNDUP(J6/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="24">
+        <f t="shared" ref="L6:L11" si="5">J6-K6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <f t="shared" ref="M6:M11" si="6">J6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="24">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="3">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <f>ROUND(C12*D12/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:C4"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="M2:M4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Resources/Sheet/Book3.xlsx
+++ b/Resources/Sheet/Book3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B847B020-C3CD-4CC0-AC5C-FDE5A25AD3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FE2EF6-8997-4971-BFD8-9E52805314AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="4140" windowWidth="21600" windowHeight="12735" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoDamQuanY" sheetId="16" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
   <si>
     <t>+</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>Phòng ngự phía sau</t>
-  </si>
-  <si>
-    <t>CĐ vòng ngoài</t>
   </si>
   <si>
     <t>Dự bị cơ động</t>
@@ -1155,7 +1152,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -1191,7 +1188,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -1227,7 +1224,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -1261,7 +1258,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -1297,7 +1294,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3">
         <f>C5</f>
@@ -1312,7 +1309,7 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="2"/>
@@ -1349,7 +1346,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -1364,22 +1361,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="D2" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="E2" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="F2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="G2" s="32" t="s">
         <v>26</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>27</v>
       </c>
       <c r="H2" s="32"/>
     </row>
@@ -1391,18 +1388,18 @@
       <c r="E3" s="32"/>
       <c r="F3" s="32"/>
       <c r="G3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18.75">
       <c r="A4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1416,10 +1413,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1442,10 +1439,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1468,10 +1465,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1494,10 +1491,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -1520,10 +1517,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1546,10 +1543,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -1572,10 +1569,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="8">
         <v>0</v>
@@ -1598,10 +1595,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -1624,10 +1621,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="8">
         <v>0</v>
@@ -1650,10 +1647,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="D14" s="8">
         <v>0</v>
@@ -1673,10 +1670,10 @@
     </row>
     <row r="15" spans="1:8" ht="18.75">
       <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8">
@@ -1697,10 +1694,10 @@
     </row>
     <row r="16" spans="1:8" ht="18.75">
       <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8">
@@ -1724,10 +1721,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="8">
         <v>0</v>
@@ -1750,10 +1747,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="8">
         <v>0</v>
@@ -1776,7 +1773,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
@@ -1802,7 +1799,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>2</v>
@@ -1828,10 +1825,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="D21" s="8">
         <v>0</v>
@@ -1851,10 +1848,10 @@
     </row>
     <row r="22" spans="1:8" ht="18.75">
       <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8">
@@ -1878,10 +1875,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="D23" s="8">
         <v>0</v>
@@ -1904,10 +1901,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="8">
         <v>0</v>
@@ -1930,10 +1927,10 @@
         <v>9</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="8">
         <v>0</v>
@@ -1956,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="D26" s="8">
         <v>0</v>
@@ -1979,10 +1976,10 @@
     </row>
     <row r="27" spans="1:8" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8">
@@ -2006,10 +2003,10 @@
         <v>12</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" s="8">
         <v>0</v>
@@ -2029,13 +2026,13 @@
     </row>
     <row r="29" spans="1:8" ht="18.75">
       <c r="A29" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="D29" s="8">
         <v>0</v>
@@ -2055,7 +2052,7 @@
     </row>
     <row r="30" spans="1:8" ht="18.75">
       <c r="A30" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
@@ -2068,7 +2065,7 @@
     <row r="31" spans="1:8" ht="18.75">
       <c r="A31" s="13"/>
       <c r="B31" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" s="12">
         <v>20</v>
@@ -2082,7 +2079,7 @@
     <row r="32" spans="1:8" ht="37.5">
       <c r="A32" s="13"/>
       <c r="B32" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2094,7 +2091,7 @@
     <row r="33" spans="1:8" ht="18.75">
       <c r="A33" s="13"/>
       <c r="B33" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="12">
         <v>8</v>
@@ -2108,7 +2105,7 @@
     <row r="34" spans="1:8" ht="18.75">
       <c r="A34" s="13"/>
       <c r="B34" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="12">
         <v>50</v>
@@ -2122,7 +2119,7 @@
     <row r="35" spans="1:8" ht="18.75">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="12">
         <v>1.5</v>
@@ -2135,7 +2132,7 @@
     </row>
     <row r="36" spans="1:8" ht="18.75">
       <c r="A36" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12"/>
@@ -2148,7 +2145,7 @@
     <row r="37" spans="1:8" ht="18.75">
       <c r="A37" s="13"/>
       <c r="B37" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="12">
         <v>8</v>
@@ -2162,7 +2159,7 @@
     <row r="38" spans="1:8" ht="18.75">
       <c r="A38" s="13"/>
       <c r="B38" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="12">
         <v>7.5</v>
@@ -2176,7 +2173,7 @@
     <row r="39" spans="1:8" ht="18.75">
       <c r="A39" s="13"/>
       <c r="B39" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="12">
         <v>9</v>
@@ -2190,7 +2187,7 @@
     <row r="40" spans="1:8" ht="18.75">
       <c r="A40" s="13"/>
       <c r="B40" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
@@ -2227,7 +2224,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" thickBot="1">
       <c r="A1" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1">
@@ -2235,18 +2232,18 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="35" t="s">
         <v>80</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>81</v>
       </c>
       <c r="E2" s="36"/>
       <c r="F2" s="37"/>
       <c r="G2" s="35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="36"/>
       <c r="I2" s="37"/>
@@ -2256,30 +2253,30 @@
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
       <c r="D3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>85</v>
-      </c>
       <c r="G3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="I3" s="19" t="s">
         <v>84</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="19.5" thickBot="1">
       <c r="A4" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="17"/>
@@ -2292,7 +2289,7 @@
     <row r="5" spans="1:9" ht="19.5" thickBot="1">
       <c r="A5" s="16"/>
       <c r="B5" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="17"/>
@@ -2307,10 +2304,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>86</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>87</v>
       </c>
       <c r="D6" s="22">
         <f>F6-E6</f>
@@ -2340,10 +2337,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="22">
         <f t="shared" ref="D7:D18" si="0">F7-E7</f>
@@ -2373,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>2</v>
@@ -2406,7 +2403,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>2</v>
@@ -2439,10 +2436,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
@@ -2470,7 +2467,7 @@
     <row r="11" spans="1:9" ht="19.5" thickBot="1">
       <c r="A11" s="20"/>
       <c r="B11" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -2491,10 +2488,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>57</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>58</v>
       </c>
       <c r="D12" s="22">
         <f t="shared" si="0"/>
@@ -2524,10 +2521,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
@@ -2557,10 +2554,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
@@ -2590,10 +2587,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="22">
         <f t="shared" si="0"/>
@@ -2621,7 +2618,7 @@
     <row r="16" spans="1:9" ht="19.5" thickBot="1">
       <c r="A16" s="20"/>
       <c r="B16" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
@@ -2642,10 +2639,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
@@ -2672,13 +2669,13 @@
     </row>
     <row r="18" spans="1:9" ht="19.5" thickBot="1">
       <c r="A18" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="22" t="s">
         <v>66</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>67</v>
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
@@ -2717,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE6020-7C21-4FFE-A7B3-EC73B1C2094F}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2740,7 +2737,7 @@
       <c r="I1" s="29"/>
       <c r="J1" s="30"/>
       <c r="K1" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L1" s="39"/>
       <c r="M1" s="40"/>
@@ -2763,13 +2760,13 @@
         <v>0</v>
       </c>
       <c r="K2" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="41" t="s">
-        <v>96</v>
-      </c>
       <c r="M2" s="41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2878,33 +2875,33 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="3">
-        <f t="shared" ref="E6:E11" si="0">ROUND(C6*D6/100,0)</f>
+        <f t="shared" ref="E6:E9" si="0">ROUND(C6*D6/100,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
-        <f t="shared" ref="G6:G11" si="1">ROUND(E6*F6/100,0)</f>
+        <f t="shared" ref="G6:G9" si="1">ROUND(E6*F6/100,0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:I11" si="2">ROUND(H6*C6/100,0)</f>
+        <f t="shared" ref="I6:I9" si="2">ROUND(H6*C6/100,0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" ref="J6:J11" si="3">E6+I6</f>
+        <f t="shared" ref="J6:J9" si="3">E6+I6</f>
         <v>0</v>
       </c>
       <c r="K6" s="24">
-        <f t="shared" ref="K6:K11" si="4">ROUNDUP(J6/2,0)</f>
+        <f t="shared" ref="K6:K9" si="4">ROUNDUP(J6/2,0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="24">
-        <f t="shared" ref="L6:L11" si="5">J6-K6</f>
+        <f t="shared" ref="L6:L9" si="5">J6-K6</f>
         <v>0</v>
       </c>
       <c r="M6" s="24">
-        <f t="shared" ref="M6:M11" si="6">J6</f>
+        <f t="shared" ref="M6:M9" si="6">J6</f>
         <v>0</v>
       </c>
     </row>
@@ -2950,7 +2947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="24">
+    <row r="8" spans="1:13" ht="36">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -2992,12 +2989,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="24">
+    <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -3035,115 +3032,31 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="24">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
+      <c r="A10" s="2">
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5"/>
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
       <c r="E10" s="3">
-        <f t="shared" si="0"/>
+        <f>ROUND(C10*D10/100,0)</f>
         <v>0</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="24">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="24">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24">
-      <c r="A12" s="2">
-        <v>2</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3">
-        <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <f>ROUND(C12*D12/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Resources/Sheet/Book3.xlsx
+++ b/Resources/Sheet/Book3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FE2EF6-8997-4971-BFD8-9E52805314AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FD5D47-53B4-4DA3-85CB-4C1A7709644C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoDamQuanY" sheetId="16" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="PhanCapVCHC" sheetId="18" r:id="rId3"/>
     <sheet name="KeHoachBaoDamQuanY" sheetId="20" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -336,7 +339,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +418,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -636,7 +645,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -701,12 +710,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -716,6 +725,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -737,24 +764,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -770,6 +781,48 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Giao diện"/>
+      <sheetName val="QSTBKT"/>
+      <sheetName val="TinhHinhVC"/>
+      <sheetName val="ChiLenhHCKT"/>
+      <sheetName val="DuKienKLVatChat"/>
+      <sheetName val="PhanCapVCHC"/>
+      <sheetName val="DuKienTiLeTBBB"/>
+      <sheetName val="ToChucLucLuong"/>
+      <sheetName val="BaoDamVKTBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="TiLeVuKhiHuHong"/>
+      <sheetName val="KhoiLuongVanTai"/>
+      <sheetName val="KeHoachVanChuyen"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1031,7 +1084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68878A65-A8E3-488E-8D20-235E1B05D76B}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="25" t="s">
@@ -1054,9 +1107,9 @@
       <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="28" t="s">
         <v>6</v>
       </c>
@@ -1072,9 +1125,9 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1091,22 +1144,22 @@
       <c r="I3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
       <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1337,56 +1390,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDF17EA-1061-464B-883E-6391396F7EEA}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999">
+      <c r="A1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" spans="1:8" ht="18.75">
-      <c r="A2" s="32" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+    </row>
+    <row r="2" spans="1:8" ht="17.399999999999999">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="32"/>
-    </row>
-    <row r="3" spans="1:8" ht="37.5">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="3" spans="1:8" ht="17.399999999999999">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="6" t="s">
         <v>27</v>
       </c>
@@ -1394,7 +1447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75">
+    <row r="4" spans="1:8" ht="18">
       <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
@@ -1408,7 +1461,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75">
+    <row r="5" spans="1:8" ht="18">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -1434,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75">
+    <row r="6" spans="1:8" ht="18">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1460,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75">
+    <row r="7" spans="1:8" ht="18">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -1486,7 +1539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75">
+    <row r="8" spans="1:8" ht="18">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1512,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75">
+    <row r="9" spans="1:8" ht="18">
       <c r="A9" s="8">
         <v>5</v>
       </c>
@@ -1538,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75">
+    <row r="10" spans="1:8" ht="18">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1564,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75">
+    <row r="11" spans="1:8" ht="18">
       <c r="A11" s="8">
         <v>7</v>
       </c>
@@ -1590,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75">
+    <row r="12" spans="1:8" ht="18">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -1616,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75">
+    <row r="13" spans="1:8" ht="18">
       <c r="A13" s="8">
         <v>9</v>
       </c>
@@ -1642,7 +1695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75">
+    <row r="14" spans="1:8" ht="18">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -1668,7 +1721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75">
+    <row r="15" spans="1:8" ht="18">
       <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
@@ -1692,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75">
+    <row r="16" spans="1:8" ht="18">
       <c r="A16" s="6" t="s">
         <v>45</v>
       </c>
@@ -1716,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75">
+    <row r="17" spans="1:8" ht="18">
       <c r="A17" s="8">
         <v>1</v>
       </c>
@@ -1742,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75">
+    <row r="18" spans="1:8" ht="18">
       <c r="A18" s="8">
         <v>2</v>
       </c>
@@ -1768,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75">
+    <row r="19" spans="1:8" ht="18">
       <c r="A19" s="8">
         <v>3</v>
       </c>
@@ -1794,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75">
+    <row r="20" spans="1:8" ht="18">
       <c r="A20" s="8">
         <v>4</v>
       </c>
@@ -1820,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75">
+    <row r="21" spans="1:8" ht="18">
       <c r="A21" s="8">
         <v>5</v>
       </c>
@@ -1846,7 +1899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75">
+    <row r="22" spans="1:8" ht="18">
       <c r="A22" s="6" t="s">
         <v>54</v>
       </c>
@@ -1870,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75">
+    <row r="23" spans="1:8" ht="18">
       <c r="A23" s="8">
         <v>7</v>
       </c>
@@ -1896,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75">
+    <row r="24" spans="1:8" ht="18">
       <c r="A24" s="8">
         <v>8</v>
       </c>
@@ -1922,7 +1975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75">
+    <row r="25" spans="1:8" ht="18">
       <c r="A25" s="8">
         <v>9</v>
       </c>
@@ -1948,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75">
+    <row r="26" spans="1:8" ht="18">
       <c r="A26" s="8">
         <v>10</v>
       </c>
@@ -1974,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75">
+    <row r="27" spans="1:8" ht="18">
       <c r="A27" s="6" t="s">
         <v>54</v>
       </c>
@@ -1998,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75">
+    <row r="28" spans="1:8" ht="18">
       <c r="A28" s="8">
         <v>12</v>
       </c>
@@ -2024,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75">
+    <row r="29" spans="1:8" ht="18">
       <c r="A29" s="6" t="s">
         <v>64</v>
       </c>
@@ -2050,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75">
+    <row r="30" spans="1:8" ht="18">
       <c r="A30" s="10" t="s">
         <v>67</v>
       </c>
@@ -2062,7 +2115,7 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
     </row>
-    <row r="31" spans="1:8" ht="18.75">
+    <row r="31" spans="1:8" ht="18">
       <c r="A31" s="13"/>
       <c r="B31" s="14" t="s">
         <v>68</v>
@@ -2076,7 +2129,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="1:8" ht="37.5">
+    <row r="32" spans="1:8" ht="18">
       <c r="A32" s="13"/>
       <c r="B32" s="14" t="s">
         <v>69</v>
@@ -2088,7 +2141,7 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
     </row>
-    <row r="33" spans="1:8" ht="18.75">
+    <row r="33" spans="1:8" ht="18">
       <c r="A33" s="13"/>
       <c r="B33" s="14" t="s">
         <v>70</v>
@@ -2102,7 +2155,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" spans="1:8" ht="18.75">
+    <row r="34" spans="1:8" ht="18">
       <c r="A34" s="13"/>
       <c r="B34" s="14" t="s">
         <v>71</v>
@@ -2116,7 +2169,7 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
     </row>
-    <row r="35" spans="1:8" ht="18.75">
+    <row r="35" spans="1:8" ht="18">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
         <v>72</v>
@@ -2130,7 +2183,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8" ht="18.75">
+    <row r="36" spans="1:8" ht="18">
       <c r="A36" s="10" t="s">
         <v>73</v>
       </c>
@@ -2142,7 +2195,7 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" ht="18.75">
+    <row r="37" spans="1:8" ht="18">
       <c r="A37" s="13"/>
       <c r="B37" s="14" t="s">
         <v>74</v>
@@ -2156,7 +2209,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" spans="1:8" ht="18.75">
+    <row r="38" spans="1:8" ht="18">
       <c r="A38" s="13"/>
       <c r="B38" s="14" t="s">
         <v>75</v>
@@ -2170,7 +2223,7 @@
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
     </row>
-    <row r="39" spans="1:8" ht="18.75">
+    <row r="39" spans="1:8" ht="18">
       <c r="A39" s="13"/>
       <c r="B39" s="14" t="s">
         <v>76</v>
@@ -2184,7 +2237,7 @@
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
     </row>
-    <row r="40" spans="1:8" ht="18.75">
+    <row r="40" spans="1:8" ht="18">
       <c r="A40" s="13"/>
       <c r="B40" s="14" t="s">
         <v>77</v>
@@ -2216,9 +2269,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D025E2D6-EA1E-4D0C-8531-FB2A59F3BA70}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2227,31 +2280,31 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1">
-      <c r="A2" s="33" t="s">
+    <row r="2" spans="1:9" ht="18" thickBot="1">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="35" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="37"/>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
+    </row>
+    <row r="3" spans="1:9" ht="18" thickBot="1">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
       <c r="D3" s="17" t="s">
         <v>82</v>
       </c>
@@ -2271,7 +2324,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1">
+    <row r="4" spans="1:9" ht="18" thickBot="1">
       <c r="A4" s="16" t="s">
         <v>29</v>
       </c>
@@ -2286,7 +2339,7 @@
       <c r="H4" s="18"/>
       <c r="I4" s="19"/>
     </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1">
+    <row r="5" spans="1:9" ht="18" thickBot="1">
       <c r="A5" s="16"/>
       <c r="B5" s="19" t="s">
         <v>46</v>
@@ -2299,7 +2352,7 @@
       <c r="H5" s="18"/>
       <c r="I5" s="19"/>
     </row>
-    <row r="6" spans="1:9" ht="19.5" thickBot="1">
+    <row r="6" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
@@ -2332,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1">
+    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
@@ -2365,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1">
+    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
@@ -2398,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" thickBot="1">
+    <row r="9" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
@@ -2431,7 +2484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" thickBot="1">
+    <row r="10" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
@@ -2464,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="19.5" thickBot="1">
+    <row r="11" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A11" s="20"/>
       <c r="B11" s="19" t="s">
         <v>55</v>
@@ -2483,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" thickBot="1">
+    <row r="12" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
@@ -2516,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" thickBot="1">
+    <row r="13" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
@@ -2549,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" thickBot="1">
+    <row r="14" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
@@ -2582,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" thickBot="1">
+    <row r="15" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
@@ -2615,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="19.5" thickBot="1">
+    <row r="16" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A16" s="20"/>
       <c r="B16" s="19" t="s">
         <v>91</v>
@@ -2634,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.5" thickBot="1">
+    <row r="17" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A17" s="20">
         <v>11</v>
       </c>
@@ -2667,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="19.5" thickBot="1">
+    <row r="18" spans="1:9" ht="18.600000000000001" thickBot="1">
       <c r="A18" s="20" t="s">
         <v>92</v>
       </c>
@@ -2715,7 +2768,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE6020-7C21-4FFE-A7B3-EC73B1C2094F}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="25" t="s">
@@ -2736,16 +2789,16 @@
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
       <c r="J1" s="30"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
       <c r="D2" s="28" t="s">
         <v>6</v>
       </c>
@@ -2759,20 +2812,20 @@
       <c r="J2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="34" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="25" t="s">
         <v>2</v>
       </c>
@@ -2789,31 +2842,31 @@
       <c r="I3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="26"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
       <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
@@ -2822,32 +2875,33 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" s="44">
+        <v>0</v>
+      </c>
+      <c r="D5" s="45">
+        <f>[1]ChiLenhHCKT!D31</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="44">
         <f>ROUND(C5*D5/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <f>ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <f>ROUND(H5*C5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <f>E5+I5</f>
+      <c r="F5" s="45">
+        <v>20</v>
+      </c>
+      <c r="G5" s="44">
+        <f t="shared" ref="G5:G10" si="0">ROUND(E5*F5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="44">
+        <f t="shared" ref="I5:I10" si="1">ROUND(H5*C5/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="44">
+        <f t="shared" ref="J5:J10" si="2">ROUND(E5+I5,0)</f>
         <v>0</v>
       </c>
       <c r="K5" s="24">
@@ -2870,38 +2924,44 @@
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3">
-        <f t="shared" ref="E6:E9" si="0">ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="3">
-        <f t="shared" ref="G6:G9" si="1">ROUND(E6*F6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3">
-        <f t="shared" ref="I6:I9" si="2">ROUND(H6*C6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" ref="J6:J9" si="3">E6+I6</f>
+      <c r="C6" s="44">
+        <v>0</v>
+      </c>
+      <c r="D6" s="45">
+        <v>20</v>
+      </c>
+      <c r="E6" s="44">
+        <f>ROUND(C6*D6/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="45">
+        <v>20</v>
+      </c>
+      <c r="G6" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="44">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K6" s="24">
-        <f t="shared" ref="K6:K9" si="4">ROUNDUP(J6/2,0)</f>
+        <f t="shared" ref="K6:K10" si="3">ROUNDUP(J6/2,0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="24">
-        <f t="shared" ref="L6:L9" si="5">J6-K6</f>
+        <f t="shared" ref="L6:L10" si="4">J6-K6</f>
         <v>0</v>
       </c>
       <c r="M6" s="24">
-        <f t="shared" ref="M6:M9" si="6">J6</f>
+        <f t="shared" ref="M6:M10" si="5">J6</f>
         <v>0</v>
       </c>
     </row>
@@ -2912,80 +2972,92 @@
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="3">
+      <c r="C7" s="44">
+        <v>0</v>
+      </c>
+      <c r="D7" s="45">
+        <v>19</v>
+      </c>
+      <c r="E7" s="44">
+        <f>ROUND(C7*D7/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="45">
+        <v>20</v>
+      </c>
+      <c r="G7" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="3">
+      <c r="H7" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="3">
+      <c r="J7" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K7" s="24">
+      <c r="L7" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L7" s="24">
+      <c r="M7" s="24">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M7" s="24">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="36">
+    </row>
+    <row r="8" spans="1:13" ht="24">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="3">
+      <c r="C8" s="44">
+        <v>0</v>
+      </c>
+      <c r="D8" s="45">
+        <v>17</v>
+      </c>
+      <c r="E8" s="44">
+        <f>ROUND(C8*D8/100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="45">
+        <v>20</v>
+      </c>
+      <c r="G8" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="3">
+      <c r="H8" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="3">
+      <c r="J8" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="24">
+      <c r="L8" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="24">
+      <c r="M8" s="24">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="24">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -2996,38 +3068,45 @@
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="3">
+      <c r="C9" s="44">
+        <v>-1</v>
+      </c>
+      <c r="D9" s="44">
+        <f>ROUND(E9/C9*100,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="44">
+        <f>E5-E6-E7-E8</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="45">
+        <v>20</v>
+      </c>
+      <c r="G9" s="44">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="3">
+      <c r="H9" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="3">
+      <c r="J9" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="24">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="24">
+      <c r="L9" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="24">
+      <c r="M9" s="24">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="24">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -3038,25 +3117,47 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="44">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="44">
+        <v>0</v>
+      </c>
+      <c r="E10" s="44">
         <f>ROUND(C10*D10/100,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
+      <c r="F10" s="45">
+        <v>20</v>
+      </c>
+      <c r="G10" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Resources/Sheet/Book3.xlsx
+++ b/Resources/Sheet/Book3.xlsx
@@ -5,22 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FD5D47-53B4-4DA3-85CB-4C1A7709644C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B7BC97-CBAC-41C5-8BD8-2568683F3594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaoDamQuanY" sheetId="16" r:id="rId1"/>
     <sheet name="ChiLenhHCKT" sheetId="17" r:id="rId2"/>
     <sheet name="PhanCapVCHC" sheetId="18" r:id="rId3"/>
-    <sheet name="KeHoachBaoDamQuanY" sheetId="20" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>+</t>
   </si>
@@ -80,15 +76,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Hướng chủ yếu</t>
-  </si>
-  <si>
-    <t>Hướng thứ yếu</t>
-  </si>
-  <si>
-    <t>Phòng ngự phía sau</t>
-  </si>
-  <si>
     <t>Dự bị cơ động</t>
   </si>
   <si>
@@ -318,15 +305,6 @@
   </si>
   <si>
     <t>II.</t>
-  </si>
-  <si>
-    <t>Phân bổ chuyển thương</t>
-  </si>
-  <si>
-    <t>Cáng bộ</t>
-  </si>
-  <si>
-    <t>Tự đi</t>
   </si>
   <si>
     <t>Hướng Chủ yếu</t>
@@ -339,7 +317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,22 +389,8 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -460,12 +424,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -706,7 +664,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -725,24 +682,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -764,8 +703,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -781,48 +718,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Giao diện"/>
-      <sheetName val="QSTBKT"/>
-      <sheetName val="TinhHinhVC"/>
-      <sheetName val="ChiLenhHCKT"/>
-      <sheetName val="DuKienKLVatChat"/>
-      <sheetName val="PhanCapVCHC"/>
-      <sheetName val="DuKienTiLeTBBB"/>
-      <sheetName val="ToChucLucLuong"/>
-      <sheetName val="BaoDamVKTBKT"/>
-      <sheetName val="Đạn"/>
-      <sheetName val="VCHC, VTKT"/>
-      <sheetName val="TiLeVuKhiHuHong"/>
-      <sheetName val="KhoiLuongVanTai"/>
-      <sheetName val="KeHoachVanChuyen"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1084,82 +979,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68878A65-A8E3-488E-8D20-235E1B05D76B}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="30"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="28" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="28" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="29"/>
+      <c r="J2" s="24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="29"/>
+      <c r="H3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="27"/>
+      <c r="J3" s="26"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
       <c r="J4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1205,7 +1100,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -1241,7 +1136,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -1277,7 +1172,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -1311,7 +1206,7 @@
     <row r="9" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -1347,7 +1242,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <f>C5</f>
@@ -1362,7 +1257,7 @@
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="2"/>
@@ -1390,69 +1285,69 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDF17EA-1061-464B-883E-6391396F7EEA}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:8" ht="18.75">
+      <c r="A1" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+    </row>
+    <row r="2" spans="1:8" ht="18.75">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:8" ht="17.399999999999999">
-      <c r="A2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38" t="s">
+      <c r="E2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="F2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="G2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="37.5">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="H3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="38" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="18.75">
+      <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="38"/>
-    </row>
-    <row r="3" spans="1:8" ht="17.399999999999999">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18">
-      <c r="A4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1461,15 +1356,15 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" ht="18">
+    <row r="5" spans="1:8" ht="18.75">
       <c r="A5" s="8">
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1487,15 +1382,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18">
+    <row r="6" spans="1:8" ht="18.75">
       <c r="A6" s="8">
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1513,15 +1408,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18">
+    <row r="7" spans="1:8" ht="18.75">
       <c r="A7" s="8">
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1539,15 +1434,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18">
+    <row r="8" spans="1:8" ht="18.75">
       <c r="A8" s="8">
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8">
         <v>0</v>
@@ -1565,15 +1460,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18">
+    <row r="9" spans="1:8" ht="18.75">
       <c r="A9" s="8">
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1591,15 +1486,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18">
+    <row r="10" spans="1:8" ht="18.75">
       <c r="A10" s="8">
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -1617,15 +1512,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18">
+    <row r="11" spans="1:8" ht="18.75">
       <c r="A11" s="8">
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" s="8">
         <v>0</v>
@@ -1643,15 +1538,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18">
+    <row r="12" spans="1:8" ht="18.75">
       <c r="A12" s="8">
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -1669,15 +1564,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18">
+    <row r="13" spans="1:8" ht="18.75">
       <c r="A13" s="8">
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="8">
         <v>0</v>
@@ -1695,38 +1590,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18">
+    <row r="14" spans="1:8" ht="18.75">
       <c r="A14" s="8">
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75">
+      <c r="A15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18">
-      <c r="A15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8">
@@ -1745,12 +1640,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18">
+    <row r="16" spans="1:8" ht="18.75">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8">
@@ -1769,15 +1664,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18">
+    <row r="17" spans="1:8" ht="18.75">
       <c r="A17" s="8">
         <v>1</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="8">
         <v>0</v>
@@ -1795,15 +1690,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18">
+    <row r="18" spans="1:8" ht="18.75">
       <c r="A18" s="8">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="8">
         <v>0</v>
@@ -1821,12 +1716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18">
+    <row r="19" spans="1:8" ht="18.75">
       <c r="A19" s="8">
         <v>3</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
@@ -1847,12 +1742,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18">
+    <row r="20" spans="1:8" ht="18.75">
       <c r="A20" s="8">
         <v>4</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>2</v>
@@ -1873,38 +1768,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18">
+    <row r="21" spans="1:8" ht="18.75">
       <c r="A21" s="8">
         <v>5</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18.75">
+      <c r="A22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18">
-      <c r="A22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8">
@@ -1923,15 +1818,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18">
+    <row r="23" spans="1:8" ht="18.75">
       <c r="A23" s="8">
         <v>7</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D23" s="8">
         <v>0</v>
@@ -1949,15 +1844,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18">
+    <row r="24" spans="1:8" ht="18.75">
       <c r="A24" s="8">
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" s="8">
         <v>0</v>
@@ -1975,15 +1870,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18">
+    <row r="25" spans="1:8" ht="18.75">
       <c r="A25" s="8">
         <v>9</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D25" s="8">
         <v>0</v>
@@ -2001,15 +1896,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18">
+    <row r="26" spans="1:8" ht="18.75">
       <c r="A26" s="8">
         <v>10</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D26" s="8">
         <v>0</v>
@@ -2027,12 +1922,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18">
+    <row r="27" spans="1:8" ht="18.75">
       <c r="A27" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8">
@@ -2051,61 +1946,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18">
+    <row r="28" spans="1:8" ht="18.75">
       <c r="A28" s="8">
         <v>12</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="18.75">
+      <c r="A29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0</v>
-      </c>
-      <c r="F28" s="8">
-        <v>0</v>
-      </c>
-      <c r="G28" s="8">
-        <v>0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="18">
-      <c r="A29" s="6" t="s">
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="18.75">
+      <c r="A30" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0</v>
-      </c>
-      <c r="F29" s="8">
-        <v>0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="18">
-      <c r="A30" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
@@ -2115,10 +2010,10 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
     </row>
-    <row r="31" spans="1:8" ht="18">
+    <row r="31" spans="1:8" ht="18.75">
       <c r="A31" s="13"/>
       <c r="B31" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C31" s="12">
         <v>20</v>
@@ -2129,10 +2024,10 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="1:8" ht="18">
+    <row r="32" spans="1:8" ht="37.5">
       <c r="A32" s="13"/>
       <c r="B32" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2141,10 +2036,10 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
     </row>
-    <row r="33" spans="1:8" ht="18">
+    <row r="33" spans="1:8" ht="18.75">
       <c r="A33" s="13"/>
       <c r="B33" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" s="12">
         <v>8</v>
@@ -2155,10 +2050,10 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" spans="1:8" ht="18">
+    <row r="34" spans="1:8" ht="18.75">
       <c r="A34" s="13"/>
       <c r="B34" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C34" s="12">
         <v>50</v>
@@ -2169,10 +2064,10 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
     </row>
-    <row r="35" spans="1:8" ht="18">
+    <row r="35" spans="1:8" ht="18.75">
       <c r="A35" s="13"/>
       <c r="B35" s="14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C35" s="12">
         <v>1.5</v>
@@ -2183,9 +2078,9 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8" ht="18">
+    <row r="36" spans="1:8" ht="18.75">
       <c r="A36" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="12"/>
@@ -2195,10 +2090,10 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" ht="18">
+    <row r="37" spans="1:8" ht="18.75">
       <c r="A37" s="13"/>
       <c r="B37" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C37" s="12">
         <v>8</v>
@@ -2209,10 +2104,10 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" spans="1:8" ht="18">
+    <row r="38" spans="1:8" ht="18.75">
       <c r="A38" s="13"/>
       <c r="B38" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C38" s="12">
         <v>7.5</v>
@@ -2223,10 +2118,10 @@
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
     </row>
-    <row r="39" spans="1:8" ht="18">
+    <row r="39" spans="1:8" ht="18.75">
       <c r="A39" s="13"/>
       <c r="B39" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C39" s="12">
         <v>9</v>
@@ -2237,10 +2132,10 @@
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
     </row>
-    <row r="40" spans="1:8" ht="18">
+    <row r="40" spans="1:8" ht="18.75">
       <c r="A40" s="13"/>
       <c r="B40" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
@@ -2269,67 +2164,67 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D025E2D6-EA1E-4D0C-8531-FB2A59F3BA70}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" thickBot="1">
       <c r="A1" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="34" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="18" thickBot="1">
-      <c r="A2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="41" t="s">
+      <c r="E3" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="41" t="s">
+      <c r="F3" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:9" ht="18" thickBot="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>84</v>
-      </c>
       <c r="G3" s="17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18" thickBot="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" thickBot="1">
       <c r="A4" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="17"/>
@@ -2339,10 +2234,10 @@
       <c r="H4" s="18"/>
       <c r="I4" s="19"/>
     </row>
-    <row r="5" spans="1:9" ht="18" thickBot="1">
+    <row r="5" spans="1:9" ht="19.5" thickBot="1">
       <c r="A5" s="16"/>
       <c r="B5" s="19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="17"/>
@@ -2352,15 +2247,15 @@
       <c r="H5" s="18"/>
       <c r="I5" s="19"/>
     </row>
-    <row r="6" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="6" spans="1:9" ht="19.5" thickBot="1">
       <c r="A6" s="20">
         <v>1</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" s="22">
         <f>F6-E6</f>
@@ -2385,15 +2280,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="7" spans="1:9" ht="19.5" thickBot="1">
       <c r="A7" s="20">
         <v>2</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7" s="22">
         <f t="shared" ref="D7:D18" si="0">F7-E7</f>
@@ -2418,12 +2313,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="8" spans="1:9" ht="19.5" thickBot="1">
       <c r="A8" s="20">
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>2</v>
@@ -2451,12 +2346,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="9" spans="1:9" ht="19.5" thickBot="1">
       <c r="A9" s="20">
         <v>4</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>2</v>
@@ -2484,15 +2379,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="10" spans="1:9" ht="19.5" thickBot="1">
       <c r="A10" s="20">
         <v>5</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D10" s="22">
         <f t="shared" si="0"/>
@@ -2517,10 +2412,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="11" spans="1:9" ht="19.5" thickBot="1">
       <c r="A11" s="20"/>
       <c r="B11" s="19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
@@ -2536,15 +2431,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="12" spans="1:9" ht="19.5" thickBot="1">
       <c r="A12" s="20">
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D12" s="22">
         <f t="shared" si="0"/>
@@ -2569,15 +2464,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="13" spans="1:9" ht="19.5" thickBot="1">
       <c r="A13" s="20">
         <v>8</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" s="22">
         <f t="shared" si="0"/>
@@ -2602,15 +2497,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="14" spans="1:9" ht="19.5" thickBot="1">
       <c r="A14" s="20">
         <v>9</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D14" s="22">
         <f t="shared" si="0"/>
@@ -2635,15 +2530,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="15" spans="1:9" ht="19.5" thickBot="1">
       <c r="A15" s="20">
         <v>10</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" s="22">
         <f t="shared" si="0"/>
@@ -2668,10 +2563,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="16" spans="1:9" ht="19.5" thickBot="1">
       <c r="A16" s="20"/>
       <c r="B16" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
@@ -2687,15 +2582,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="17" spans="1:9" ht="19.5" thickBot="1">
       <c r="A17" s="20">
         <v>11</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="22">
         <f t="shared" si="0"/>
@@ -2720,15 +2615,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18.600000000000001" thickBot="1">
+    <row r="18" spans="1:9" ht="19.5" thickBot="1">
       <c r="A18" s="20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D18" s="22">
         <f t="shared" si="0"/>
@@ -2763,421 +2658,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24DE6020-7C21-4FFE-A7B3-EC73B1C2094F}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="33"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="2">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="44">
-        <v>0</v>
-      </c>
-      <c r="D5" s="45">
-        <f>[1]ChiLenhHCKT!D31</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="44">
-        <f>ROUND(C5*D5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="45">
-        <v>20</v>
-      </c>
-      <c r="G5" s="44">
-        <f t="shared" ref="G5:G10" si="0">ROUND(E5*F5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I5" s="44">
-        <f t="shared" ref="I5:I10" si="1">ROUND(H5*C5/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="44">
-        <f t="shared" ref="J5:J10" si="2">ROUND(E5+I5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="24">
-        <f>ROUNDUP(J5/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="24">
-        <f>J5-K5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="24">
-        <f>J5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="44">
-        <v>0</v>
-      </c>
-      <c r="D6" s="45">
-        <v>20</v>
-      </c>
-      <c r="E6" s="44">
-        <f>ROUND(C6*D6/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="45">
-        <v>20</v>
-      </c>
-      <c r="G6" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="24">
-        <f t="shared" ref="K6:K10" si="3">ROUNDUP(J6/2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="24">
-        <f t="shared" ref="L6:L10" si="4">J6-K6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="24">
-        <f t="shared" ref="M6:M10" si="5">J6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="44">
-        <v>0</v>
-      </c>
-      <c r="D7" s="45">
-        <v>19</v>
-      </c>
-      <c r="E7" s="44">
-        <f>ROUND(C7*D7/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="45">
-        <v>20</v>
-      </c>
-      <c r="G7" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L7" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="44">
-        <v>0</v>
-      </c>
-      <c r="D8" s="45">
-        <v>17</v>
-      </c>
-      <c r="E8" s="44">
-        <f>ROUND(C8*D8/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="45">
-        <v>20</v>
-      </c>
-      <c r="G8" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="44">
-        <v>-1</v>
-      </c>
-      <c r="D9" s="44">
-        <f>ROUND(E9/C9*100,1)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="44">
-        <f>E5-E6-E7-E8</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="45">
-        <v>20</v>
-      </c>
-      <c r="G9" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24">
-      <c r="A10" s="2">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="44">
-        <f>C5</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="44">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44">
-        <f>ROUND(C10*D10/100,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="45">
-        <v>20</v>
-      </c>
-      <c r="G10" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="24">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="24">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="M2:M4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>